--- a/Proyecto 1/ET_P1_Requisitos_v1.0.xlsx
+++ b/Proyecto 1/ET_P1_Requisitos_v1.0.xlsx
@@ -5,23 +5,25 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juanarodriguezgarcia/Desktop/Master en Big Data y Computacion en la Nube/2 SEMESTRE/Gobierno y Calidad del Dato/Trabajo parte 2/EnergyTech/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juanarodriguezgarcia/Desktop/Master en Big Data y Computacion en la Nube/2 SEMESTRE/Gobierno y Calidad del Dato/Trabajo parte 2/EnergyTech/Proyecto 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDD2317-AA8A-F545-8554-D3C859C640F7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A29AC5-B0E6-4E47-88EB-93E6C3ADF5AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="16100" windowHeight="16120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Requisitos" sheetId="4" r:id="rId1"/>
-    <sheet name="Control Versiones" sheetId="5" r:id="rId2"/>
+    <sheet name="Requisitos de negocio" sheetId="4" r:id="rId1"/>
+    <sheet name="Requisistos de datos" sheetId="6" r:id="rId2"/>
+    <sheet name="Requisitos de calidad" sheetId="7" r:id="rId3"/>
+    <sheet name="Control Versiones" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="79">
   <si>
     <t>ID</t>
   </si>
@@ -56,9 +58,6 @@
     <t xml:space="preserve">1. Requisitos de Negocio  </t>
   </si>
   <si>
-    <t>Estos definen el "qué" espera lograr la organización con el análisis predictivo.</t>
-  </si>
-  <si>
     <t xml:space="preserve">2. Requisitos de Datos  </t>
   </si>
   <si>
@@ -77,9 +76,6 @@
     <t>Histórico de Consumo</t>
   </si>
   <si>
-    <t>Base de Datos corporativa (ERP/Smart Meters).</t>
-  </si>
-  <si>
     <t>Numérico (kWh) / Time-series.</t>
   </si>
   <si>
@@ -122,9 +118,6 @@
     <t>3. Requisitos de Calidad del Dato (Data Quality Requirements)</t>
   </si>
   <si>
-    <t>Son los niveles de "salud" que deben tener los datos para que el análisis sea fiable.</t>
-  </si>
-  <si>
     <t>Dimensión</t>
   </si>
   <si>
@@ -234,13 +227,92 @@
   </si>
   <si>
     <t>Necesidad técnica del análisis predictivo</t>
+  </si>
+  <si>
+    <t>Estos definen el qué espera lograr la organización con el análisis predictivo.</t>
+  </si>
+  <si>
+    <t>Base de Datos corporativa (ERP).</t>
+  </si>
+  <si>
+    <t>Prioridad</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Registros de las mediciones de energía en kilovatios-hora (kWh). Deben ser </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Series Temporales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (datos ordenados por tiempo) para que la Inteligencia Artificial entienda cómo varía el gasto de luz a lo largo del día y las estaciones.</t>
+    </r>
+  </si>
+  <si>
+    <t>Información sobre el clima futuro (como la temperatura). Es un dato externo esencial porque el uso de calefacción o aire acondicionado depende directamente del tiempo que haga.</t>
+  </si>
+  <si>
+    <t>Listado protegido de centros esenciales como hospitales. Es fundamental para que el sistema les dé prioridad absoluta y nunca se queden sin energía ante una posible sobrecarga de la red.</t>
+  </si>
+  <si>
+    <t>Mide que no falten datos en los intervalos de tiempo. Si hay demasiados "huecos" en las lecturas de los contadores, el análisis no será real. El objetivo es que el 98% de las horas tengan su dato de consumo registrado.</t>
+  </si>
+  <si>
+    <t>Define la frescura del dato. El pronóstico del tiempo debe ser reciente (máximo 3 horas de antigüedad) porque una previsión antigua no sirve para tomar decisiones de red en tiempo real.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Asegura que cada persona sea un </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Registro de Oro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (un dato único y sin errores). Evita que clientes como "Juan Pérez" cuenten como tres personas distintas, lo que causaría un error en el cálculo de la potencia total necesaria.</t>
+    </r>
+  </si>
+  <si>
+    <t>Son los niveles de salud que deben tener los datos para que el análisis sea fiable.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -277,16 +349,69 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -294,11 +419,92 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -316,6 +522,63 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -636,78 +899,87 @@
     <col min="2" max="2" width="25.33203125" customWidth="1"/>
     <col min="4" max="4" width="32.83203125" customWidth="1"/>
     <col min="5" max="5" width="39.1640625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="20.1640625" customWidth="1"/>
+    <col min="6" max="6" width="34.33203125" customWidth="1"/>
     <col min="7" max="7" width="24.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:8" ht="38" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="6"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+    </row>
+    <row r="2" spans="1:8" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+    </row>
+    <row r="3" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="46" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="46" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="13" t="s">
         <v>6</v>
       </c>
     </row>
@@ -726,109 +998,42 @@
       <c r="F7" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="19" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>12</v>
-      </c>
+      <c r="A9" s="6"/>
       <c r="B9" s="6"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-    </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B12" s="5"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
       <c r="H12" s="8"/>
     </row>
-    <row r="13" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>25</v>
-      </c>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B13" s="5"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
       <c r="H13" s="8"/>
     </row>
-    <row r="14" spans="1:8" ht="31" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>29</v>
-      </c>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C14" s="1"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
       <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -848,95 +1053,35 @@
       <c r="H16" s="8"/>
     </row>
     <row r="18" spans="1:6" ht="19" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>32</v>
-      </c>
+      <c r="A18" s="6"/>
       <c r="B18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>33</v>
-      </c>
-    </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>47</v>
-      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C24" s="1"/>
@@ -951,64 +1096,452 @@
       <c r="F25" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B8DD864-0004-C54B-AB95-7B5E16FE4B93}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="25.33203125" customWidth="1"/>
+    <col min="4" max="4" width="32.83203125" customWidth="1"/>
+    <col min="5" max="5" width="39.1640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="20.1640625" customWidth="1"/>
+    <col min="7" max="7" width="24.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+    </row>
+    <row r="2" spans="1:9" ht="43" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+    </row>
+    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="80" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="64" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="64" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C7" s="1"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="8"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C8" s="1"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="8"/>
+    </row>
+    <row r="10" spans="1:9" ht="19" x14ac:dyDescent="0.25">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B14" s="10"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373FAC65-1975-334E-B832-D54B77039B6C}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="25.33203125" customWidth="1"/>
+    <col min="4" max="4" width="32.83203125" customWidth="1"/>
+    <col min="5" max="5" width="39.1640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="20.1640625" customWidth="1"/>
+    <col min="7" max="7" width="24.1640625" customWidth="1"/>
+    <col min="8" max="8" width="41.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="26"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="29"/>
+    </row>
+    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="61" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="77" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C88266F-C6D1-0D46-A4E3-03809250E2BD}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B2" s="9">
         <v>46120</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B3" s="9">
         <v>46120</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
